--- a/tame_output/ON/bt/strategyON_20231107.xlsx
+++ b/tame_output/ON/bt/strategyON_20231107.xlsx
@@ -610,11 +610,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,12 +623,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>2023-11-06</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>83.8%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>2023-11-06</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>20.4%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>2023-11-06</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.4%</t>
+          <t>453.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>102.5%</t>
+          <t>102.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>2023-11-06</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>98.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>25.3%</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>2023-11-06</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>133.1%</t>
+          <t>133.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1375,11 +1375,11 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>2023-11-06</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1773"/>
+  <dimension ref="A1:G1774"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42289,7 +42289,7 @@
         <v>45235</v>
       </c>
       <c r="B1773" t="n">
-        <v>3.074422267851872</v>
+        <v>3.073923642968024</v>
       </c>
       <c r="C1773" t="n">
         <v>3.057781629850306</v>
@@ -42305,6 +42305,29 @@
       </c>
       <c r="G1773" t="n">
         <v>4.363274292545007</v>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" s="2" t="n">
+        <v>45236</v>
+      </c>
+      <c r="B1774" t="n">
+        <v>3.073204449978263</v>
+      </c>
+      <c r="C1774" t="n">
+        <v>3.058531492021579</v>
+      </c>
+      <c r="D1774" t="n">
+        <v>1.548808331118808</v>
+      </c>
+      <c r="E1774" t="n">
+        <v>3.677698400155356</v>
+      </c>
+      <c r="F1774" t="n">
+        <v>2.175821104491166</v>
+      </c>
+      <c r="G1774" t="n">
+        <v>4.36402415471628</v>
       </c>
     </row>
   </sheetData>
